--- a/feedback_forms/045_health_app_development_project_evaluation_form--feedback_forms.xlsx
+++ b/feedback_forms/045_health_app_development_project_evaluation_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -772,7 +772,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rating_1</t>
+          <t>rating 1</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rating_2</t>
+          <t>rating 2</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rating_3</t>
+          <t>rating 3</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rating_4</t>
+          <t>rating 4</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rating_5</t>
+          <t>rating 5</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rating_1</t>
+          <t>rating 1</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rating_2</t>
+          <t>rating 2</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rating_3</t>
+          <t>rating 3</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rating_4</t>
+          <t>rating 4</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>rating_5</t>
+          <t>rating 5</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>rating_1</t>
+          <t>rating 1</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rating_2</t>
+          <t>rating 2</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rating_3</t>
+          <t>rating 3</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rating_4</t>
+          <t>rating 4</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rating_5</t>
+          <t>rating 5</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rating_1</t>
+          <t>rating 1</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rating_2</t>
+          <t>rating 2</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rating_3</t>
+          <t>rating 3</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rating_4</t>
+          <t>rating 4</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rating_5</t>
+          <t>rating 5</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rating_1</t>
+          <t>rating 1</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>rating_2</t>
+          <t>rating 2</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>rating_3</t>
+          <t>rating 3</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rating_4</t>
+          <t>rating 4</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rating_5</t>
+          <t>rating 5</t>
         </is>
       </c>
     </row>
